--- a/Data Files/Backoffce/GeraBoleto/GeraBoleto.xlsx
+++ b/Data Files/Backoffce/GeraBoleto/GeraBoleto.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\GeraBoleto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Backoffce\GeraBoleto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1EE59BF-B392-453B-B22C-24FA6A9EF982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr documentId="13_ncr:1_{B619F539-A42C-40A3-8915-C1C6BC64B0CA}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="11040" windowWidth="20730" xWindow="-120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-120"/>
   </bookViews>
   <sheets>
-    <sheet name="GeraBoleto" sheetId="2" r:id="rId1"/>
-    <sheet name="P1" sheetId="3" r:id="rId2"/>
+    <sheet name="GeraBoleto" r:id="rId1" sheetId="2"/>
+    <sheet name="P1" r:id="rId2" sheetId="3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">GeraBoleto!$A$1:$E$1</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">GeraBoleto!$A$1:$E$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="213">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,9 @@
     <t>linha</t>
   </si>
   <si>
+    <t>Processar</t>
+  </si>
+  <si>
     <t>sim</t>
   </si>
   <si>
@@ -64,9 +67,381 @@
     <t>473980154</t>
   </si>
   <si>
+    <t>478565646</t>
+  </si>
+  <si>
+    <t>478565653</t>
+  </si>
+  <si>
+    <t>478565661</t>
+  </si>
+  <si>
+    <t>478565679</t>
+  </si>
+  <si>
+    <t>478565687</t>
+  </si>
+  <si>
+    <t>478565695</t>
+  </si>
+  <si>
+    <t>478565703</t>
+  </si>
+  <si>
+    <t>481544927</t>
+  </si>
+  <si>
+    <t>481544935</t>
+  </si>
+  <si>
+    <t>481544943</t>
+  </si>
+  <si>
+    <t>481544950</t>
+  </si>
+  <si>
+    <t>481809841</t>
+  </si>
+  <si>
+    <t>481809858</t>
+  </si>
+  <si>
+    <t>481809866</t>
+  </si>
+  <si>
+    <t>481809874</t>
+  </si>
+  <si>
+    <t>481809882</t>
+  </si>
+  <si>
+    <t>481809890</t>
+  </si>
+  <si>
+    <t>481809908</t>
+  </si>
+  <si>
+    <t>483657479</t>
+  </si>
+  <si>
+    <t>483657487</t>
+  </si>
+  <si>
+    <t>483657495</t>
+  </si>
+  <si>
+    <t>483657503</t>
+  </si>
+  <si>
+    <t>484115576</t>
+  </si>
+  <si>
+    <t>484115584</t>
+  </si>
+  <si>
+    <t>484115592</t>
+  </si>
+  <si>
+    <t>484115600</t>
+  </si>
+  <si>
+    <t>487373941</t>
+  </si>
+  <si>
+    <t>487373958</t>
+  </si>
+  <si>
+    <t>487373966</t>
+  </si>
+  <si>
+    <t>487373974</t>
+  </si>
+  <si>
     <t>477178102</t>
   </si>
   <si>
+    <t>477178110</t>
+  </si>
+  <si>
+    <t>477178128</t>
+  </si>
+  <si>
+    <t>477178136</t>
+  </si>
+  <si>
+    <t>477178144</t>
+  </si>
+  <si>
+    <t>477178151</t>
+  </si>
+  <si>
+    <t>477178169</t>
+  </si>
+  <si>
+    <t>479490513</t>
+  </si>
+  <si>
+    <t>479490521</t>
+  </si>
+  <si>
+    <t>479490539</t>
+  </si>
+  <si>
+    <t>479490547</t>
+  </si>
+  <si>
+    <t>479490554</t>
+  </si>
+  <si>
+    <t>479490562</t>
+  </si>
+  <si>
+    <t>479490570</t>
+  </si>
+  <si>
+    <t>479490588</t>
+  </si>
+  <si>
+    <t>479490596</t>
+  </si>
+  <si>
+    <t>479490604</t>
+  </si>
+  <si>
+    <t>479490612</t>
+  </si>
+  <si>
+    <t>479490620</t>
+  </si>
+  <si>
+    <t>480153134</t>
+  </si>
+  <si>
+    <t>480153142</t>
+  </si>
+  <si>
+    <t>480153159</t>
+  </si>
+  <si>
+    <t>480153167</t>
+  </si>
+  <si>
+    <t>480278527</t>
+  </si>
+  <si>
+    <t>480278535</t>
+  </si>
+  <si>
+    <t>480278543</t>
+  </si>
+  <si>
+    <t>480278550</t>
+  </si>
+  <si>
+    <t>480633515</t>
+  </si>
+  <si>
+    <t>480633523</t>
+  </si>
+  <si>
+    <t>480633531</t>
+  </si>
+  <si>
+    <t>480633549</t>
+  </si>
+  <si>
+    <t>480633556</t>
+  </si>
+  <si>
+    <t>480633564</t>
+  </si>
+  <si>
+    <t>481627813</t>
+  </si>
+  <si>
+    <t>481627821</t>
+  </si>
+  <si>
+    <t>481627839</t>
+  </si>
+  <si>
+    <t>481627847</t>
+  </si>
+  <si>
+    <t>484374892</t>
+  </si>
+  <si>
+    <t>483600180</t>
+  </si>
+  <si>
+    <t>483203456</t>
+  </si>
+  <si>
+    <t>483203464</t>
+  </si>
+  <si>
+    <t>483203472</t>
+  </si>
+  <si>
+    <t>483203480</t>
+  </si>
+  <si>
+    <t>483203498</t>
+  </si>
+  <si>
+    <t>483203506</t>
+  </si>
+  <si>
+    <t>483203514</t>
+  </si>
+  <si>
+    <t>483203522</t>
+  </si>
+  <si>
+    <t>483203530</t>
+  </si>
+  <si>
+    <t>483203548</t>
+  </si>
+  <si>
+    <t>483241068</t>
+  </si>
+  <si>
+    <t>483241076</t>
+  </si>
+  <si>
+    <t>483241084</t>
+  </si>
+  <si>
+    <t>483241092</t>
+  </si>
+  <si>
+    <t>483241100</t>
+  </si>
+  <si>
+    <t>483241118</t>
+  </si>
+  <si>
+    <t>483241126</t>
+  </si>
+  <si>
+    <t>483241134</t>
+  </si>
+  <si>
+    <t>483241142</t>
+  </si>
+  <si>
+    <t>483241159</t>
+  </si>
+  <si>
+    <t>483255001</t>
+  </si>
+  <si>
+    <t>483255019</t>
+  </si>
+  <si>
+    <t>483255027</t>
+  </si>
+  <si>
+    <t>483255035</t>
+  </si>
+  <si>
+    <t>483255043</t>
+  </si>
+  <si>
+    <t>483255050</t>
+  </si>
+  <si>
+    <t>483255068</t>
+  </si>
+  <si>
+    <t>483255076</t>
+  </si>
+  <si>
+    <t>483255084</t>
+  </si>
+  <si>
+    <t>483255092</t>
+  </si>
+  <si>
+    <t>483268376</t>
+  </si>
+  <si>
+    <t>483268384</t>
+  </si>
+  <si>
+    <t>483268392</t>
+  </si>
+  <si>
+    <t>483268400</t>
+  </si>
+  <si>
+    <t>483268418</t>
+  </si>
+  <si>
+    <t>483268426</t>
+  </si>
+  <si>
+    <t>483268434</t>
+  </si>
+  <si>
+    <t>483268442</t>
+  </si>
+  <si>
+    <t>483268459</t>
+  </si>
+  <si>
+    <t>483268467</t>
+  </si>
+  <si>
+    <t>483415654</t>
+  </si>
+  <si>
+    <t>483415662</t>
+  </si>
+  <si>
+    <t>483415670</t>
+  </si>
+  <si>
+    <t>483415688</t>
+  </si>
+  <si>
+    <t>484404301</t>
+  </si>
+  <si>
+    <t>484404319</t>
+  </si>
+  <si>
+    <t>484404327</t>
+  </si>
+  <si>
+    <t>484404335</t>
+  </si>
+  <si>
+    <t>484698886</t>
+  </si>
+  <si>
+    <t>484698894</t>
+  </si>
+  <si>
+    <t>484698902</t>
+  </si>
+  <si>
+    <t>484698910</t>
+  </si>
+  <si>
+    <t>486082394</t>
+  </si>
+  <si>
+    <t>486082402</t>
+  </si>
+  <si>
+    <t>486082410</t>
+  </si>
+  <si>
+    <t>486082428</t>
+  </si>
+  <si>
     <t>Processado</t>
   </si>
   <si>
@@ -83,12 +458,223 @@
   </si>
   <si>
     <t> RECIBO VIGENTE. VENCIMENTO EM 24/10/2026</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 20/11/2026</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 20/12/2026</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 20/01/2027</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 20/02/2027</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 20/03/2027</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 20/04/2027</t>
+  </si>
+  <si>
+    <t>Alerta: Falha ao gerar boleto.  Esta seguro que é preciso duplicar o recibo? Está dentro do prazo de retorno bancário</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 05/11/2026</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 05/12/2026</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 05/01/2027</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 05/02/2027</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 05/03/2027</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 05/04/2027</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 05/05/2027</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 05/06/2027</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 05/07/2027</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 05/08/2027</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 05/09/2027</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 25/10/2026</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 08/10/2026</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 10/11/2026</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 10/12/2026</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 10/01/2027</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 09/10/2026</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 09/11/2026</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 09/12/2026</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 09/01/2027</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 28/10/2026</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 15/12/2026</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 15/01/2027</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 15/02/2027</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 15/03/2027</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 15/04/2027</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 29/10/2026</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 16/10/2026</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 16/11/2026</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 16/12/2026</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 16/01/2027</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 10/02/2027</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 10/03/2027</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 10/04/2027</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 10/05/2027</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 11/10/2026</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 14/10/2026</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 10/06/2027</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 10/07/2027</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 19/10/2026</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 15/11/2026</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 15/05/2027</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 15/06/2027</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 15/07/2027</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 22/10/2026</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 10/08/2027</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 30/10/2026</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 01/12/2026</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 01/01/2027</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 01/02/2027</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 15/10/2026</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 25/11/2026</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 25/12/2026</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 25/01/2027</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 17/10/2026</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 19/11/2026</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 19/12/2026</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 19/01/2027</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 31/10/2026</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 26/11/2026</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 26/12/2026</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 26/01/2027</t>
+  </si>
+  <si>
+    <t> RECIBO VIGENTE. VENCIMENTO EM 01/11/2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -148,32 +734,32 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="49" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="2" fontId="1" numFmtId="49" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -190,10 +776,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -228,7 +814,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -280,7 +866,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -391,21 +977,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -422,7 +1008,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -474,27 +1060,27 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G130"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="25.5703125" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="12.42578125" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="16.42578125" style="2" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="74.85546875" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="8.85546875" customWidth="1" collapsed="1"/>
-    <col min="7" max="16384" width="9.140625" style="2" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="16.7109375" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="25.5703125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="12.42578125" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="2" width="16.42578125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="74.85546875" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" width="8.85546875" collapsed="true"/>
+    <col min="7" max="16384" style="2" width="9.140625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -519,16 +1105,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>12</v>
+        <v>137</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>138</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -536,16 +1122,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>137</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>139</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -553,16 +1139,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>12</v>
+        <v>137</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>140</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -570,16 +1156,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>12</v>
+        <v>137</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>141</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -587,40 +1173,2148 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>12</v>
+        <v>137</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>142</v>
       </c>
       <c r="F6">
         <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E7" t="s">
+        <v>143</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E8" t="s">
+        <v>144</v>
+      </c>
+      <c r="F8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E9" t="s">
+        <v>145</v>
+      </c>
+      <c r="F9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E10" t="s">
+        <v>146</v>
+      </c>
+      <c r="F10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E11" t="s">
+        <v>147</v>
+      </c>
+      <c r="F11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E12" t="s">
+        <v>148</v>
+      </c>
+      <c r="F12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E13" t="s">
+        <v>149</v>
+      </c>
+      <c r="F13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E14" t="s">
+        <v>150</v>
+      </c>
+      <c r="F14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E15" t="s">
+        <v>151</v>
+      </c>
+      <c r="F15">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E16" t="s">
+        <v>152</v>
+      </c>
+      <c r="F16">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E17" t="s">
+        <v>153</v>
+      </c>
+      <c r="F17">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E18" t="s">
+        <v>154</v>
+      </c>
+      <c r="F18">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E19" t="s">
+        <v>155</v>
+      </c>
+      <c r="F19">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E20" t="s">
+        <v>156</v>
+      </c>
+      <c r="F20">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E21" t="s">
+        <v>157</v>
+      </c>
+      <c r="F21">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E22" t="s">
+        <v>158</v>
+      </c>
+      <c r="F22">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E23" t="s">
+        <v>159</v>
+      </c>
+      <c r="F23">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E24" t="s">
+        <v>160</v>
+      </c>
+      <c r="F24">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E25" t="s">
+        <v>161</v>
+      </c>
+      <c r="F25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E26" t="s">
+        <v>143</v>
+      </c>
+      <c r="F26">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E27" t="s">
+        <v>144</v>
+      </c>
+      <c r="F27">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E28" t="s">
+        <v>145</v>
+      </c>
+      <c r="F28">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E29" t="s">
+        <v>146</v>
+      </c>
+      <c r="F29">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E30" t="s">
+        <v>147</v>
+      </c>
+      <c r="F30">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E31" t="s">
+        <v>148</v>
+      </c>
+      <c r="F31">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E32" t="s">
+        <v>162</v>
+      </c>
+      <c r="F32">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E33" t="s">
+        <v>163</v>
+      </c>
+      <c r="F33">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E34" t="s">
+        <v>164</v>
+      </c>
+      <c r="F34">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E35" t="s">
+        <v>165</v>
+      </c>
+      <c r="F35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E36" t="s">
+        <v>166</v>
+      </c>
+      <c r="F36">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E37" t="s">
+        <v>167</v>
+      </c>
+      <c r="F37">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E38" t="s">
+        <v>168</v>
+      </c>
+      <c r="F38">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E39" t="s">
+        <v>169</v>
+      </c>
+      <c r="F39">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E40" t="s">
+        <v>170</v>
+      </c>
+      <c r="F40">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E41" t="s">
+        <v>171</v>
+      </c>
+      <c r="F41">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E42" t="s">
+        <v>172</v>
+      </c>
+      <c r="F42">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E43" t="s">
+        <v>173</v>
+      </c>
+      <c r="F43">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E44" t="s">
+        <v>174</v>
+      </c>
+      <c r="F44">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E45" t="s">
+        <v>175</v>
+      </c>
+      <c r="F45">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E46" t="s">
+        <v>176</v>
+      </c>
+      <c r="F46">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E47" t="s">
+        <v>143</v>
+      </c>
+      <c r="F47">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E48" t="s">
+        <v>144</v>
+      </c>
+      <c r="F48">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E49" t="s">
+        <v>145</v>
+      </c>
+      <c r="F49">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E50" t="s">
+        <v>177</v>
+      </c>
+      <c r="F50">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E51" t="s">
+        <v>178</v>
+      </c>
+      <c r="F51">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E52" t="s">
+        <v>179</v>
+      </c>
+      <c r="F52">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E53" t="s">
+        <v>180</v>
+      </c>
+      <c r="F53">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E54" t="s">
+        <v>176</v>
+      </c>
+      <c r="F54">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E55" t="s">
+        <v>164</v>
+      </c>
+      <c r="F55">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E56" t="s">
+        <v>165</v>
+      </c>
+      <c r="F56">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E57" t="s">
+        <v>181</v>
+      </c>
+      <c r="F57">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E58" t="s">
+        <v>182</v>
+      </c>
+      <c r="F58">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E59" t="s">
+        <v>183</v>
+      </c>
+      <c r="F59">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E60" t="s">
+        <v>184</v>
+      </c>
+      <c r="F60">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E61" t="s">
+        <v>185</v>
+      </c>
+      <c r="F61">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E62" t="s">
+        <v>162</v>
+      </c>
+      <c r="F62">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E63" t="s">
+        <v>186</v>
+      </c>
+      <c r="F63">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E64" t="s">
+        <v>163</v>
+      </c>
+      <c r="F64">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E65" t="s">
+        <v>164</v>
+      </c>
+      <c r="F65">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E66" t="s">
+        <v>165</v>
+      </c>
+      <c r="F66">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E67" t="s">
+        <v>181</v>
+      </c>
+      <c r="F67">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E68" t="s">
+        <v>182</v>
+      </c>
+      <c r="F68">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E69" t="s">
+        <v>183</v>
+      </c>
+      <c r="F69">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E70" t="s">
+        <v>184</v>
+      </c>
+      <c r="F70">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E71" t="s">
+        <v>187</v>
+      </c>
+      <c r="F71">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E72" t="s">
+        <v>188</v>
+      </c>
+      <c r="F72">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E73" t="s">
+        <v>189</v>
+      </c>
+      <c r="F73">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E74" t="s">
+        <v>190</v>
+      </c>
+      <c r="F74">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E75" t="s">
+        <v>171</v>
+      </c>
+      <c r="F75">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E76" t="s">
+        <v>172</v>
+      </c>
+      <c r="F76">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E77" t="s">
+        <v>173</v>
+      </c>
+      <c r="F77">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E78" t="s">
+        <v>174</v>
+      </c>
+      <c r="F78">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E79" t="s">
+        <v>175</v>
+      </c>
+      <c r="F79">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E80" t="s">
+        <v>191</v>
+      </c>
+      <c r="F80">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E81" t="s">
+        <v>192</v>
+      </c>
+      <c r="F81">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E82" t="s">
+        <v>193</v>
+      </c>
+      <c r="F82">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E83" t="s">
+        <v>177</v>
+      </c>
+      <c r="F83">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E84" t="s">
+        <v>163</v>
+      </c>
+      <c r="F84">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E85" t="s">
+        <v>164</v>
+      </c>
+      <c r="F85">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E86" t="s">
+        <v>165</v>
+      </c>
+      <c r="F86">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E87" t="s">
+        <v>181</v>
+      </c>
+      <c r="F87">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E88" t="s">
+        <v>182</v>
+      </c>
+      <c r="F88">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E89" t="s">
+        <v>183</v>
+      </c>
+      <c r="F89">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E90" t="s">
+        <v>184</v>
+      </c>
+      <c r="F90">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E91" t="s">
+        <v>187</v>
+      </c>
+      <c r="F91">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E92" t="s">
+        <v>188</v>
+      </c>
+      <c r="F92">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E93" t="s">
+        <v>194</v>
+      </c>
+      <c r="F93">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E94" t="s">
+        <v>164</v>
+      </c>
+      <c r="F94">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E95" t="s">
+        <v>165</v>
+      </c>
+      <c r="F95">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E96" t="s">
+        <v>181</v>
+      </c>
+      <c r="F96">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E97" t="s">
+        <v>182</v>
+      </c>
+      <c r="F97">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E98" t="s">
+        <v>183</v>
+      </c>
+      <c r="F98">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E99" t="s">
+        <v>184</v>
+      </c>
+      <c r="F99">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E100" t="s">
+        <v>187</v>
+      </c>
+      <c r="F100">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E101" t="s">
+        <v>188</v>
+      </c>
+      <c r="F101">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E102" t="s">
+        <v>195</v>
+      </c>
+      <c r="F102">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E103" t="s">
+        <v>196</v>
+      </c>
+      <c r="F103">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E104" t="s">
+        <v>197</v>
+      </c>
+      <c r="F104">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E105" t="s">
+        <v>198</v>
+      </c>
+      <c r="F105">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E106" t="s">
+        <v>199</v>
+      </c>
+      <c r="F106">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E107" t="s">
+        <v>200</v>
+      </c>
+      <c r="F107">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E108" t="s">
+        <v>163</v>
+      </c>
+      <c r="F108">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E109" t="s">
+        <v>164</v>
+      </c>
+      <c r="F109">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E110" t="s">
+        <v>165</v>
+      </c>
+      <c r="F110">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E111" t="s">
+        <v>196</v>
+      </c>
+      <c r="F111">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E112" t="s">
+        <v>201</v>
+      </c>
+      <c r="F112">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E113" t="s">
+        <v>202</v>
+      </c>
+      <c r="F113">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E114" t="s">
+        <v>203</v>
+      </c>
+      <c r="F114">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E115" t="s">
+        <v>204</v>
+      </c>
+      <c r="F115">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E116" t="s">
+        <v>205</v>
+      </c>
+      <c r="F116">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E117" t="s">
+        <v>206</v>
+      </c>
+      <c r="F117">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E118" t="s">
+        <v>207</v>
+      </c>
+      <c r="F118">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E119" t="s">
+        <v>208</v>
+      </c>
+      <c r="F119">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E120" t="s">
+        <v>197</v>
+      </c>
+      <c r="F120">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E121" t="s">
+        <v>198</v>
+      </c>
+      <c r="F121">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E122" t="s">
+        <v>199</v>
+      </c>
+      <c r="F122">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E123" t="s">
+        <v>142</v>
+      </c>
+      <c r="F123">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E124" t="s">
+        <v>209</v>
+      </c>
+      <c r="F124">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E125" t="s">
+        <v>210</v>
+      </c>
+      <c r="F125">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E126" t="s">
+        <v>211</v>
+      </c>
+      <c r="F126">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E127" t="s">
+        <v>185</v>
+      </c>
+      <c r="F127">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E128" t="s">
+        <v>212</v>
+      </c>
+      <c r="F128">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E129" t="s">
+        <v>197</v>
+      </c>
+      <c r="F129">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E130" t="s">
+        <v>198</v>
+      </c>
+      <c r="F130">
+        <v>128</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{66F0922E-39CC-4575-AEFA-040A62B7CE0A}"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins bottom="0.78740157480314965" footer="0.31496062992125984" header="0.31496062992125984" left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965"/>
+  <pageSetup orientation="portrait" paperSize="9" r:id="rId1"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</oddFooter>
-    <evenFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</evenFooter>
-    <firstFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</firstFooter>
+    <oddFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></oddFooter>
+    <evenFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></evenFooter>
+    <firstFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></firstFooter>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91683D9D-F452-4054-8D7A-D2744DE31F16}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91683D9D-F452-4054-8D7A-D2744DE31F16}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageMargins bottom="0.78740157499999996" footer="0.31496062000000002" header="0.31496062000000002" left="0.511811024" right="0.511811024" top="0.78740157499999996"/>
 </worksheet>
 </file>
 
